--- a/artfynd/A 20039-2024 artfynd.xlsx
+++ b/artfynd/A 20039-2024 artfynd.xlsx
@@ -777,10 +777,10 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>117658686</v>
+        <v>117658629</v>
       </c>
       <c r="B3" t="n">
-        <v>78480</v>
+        <v>57287</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>
@@ -793,21 +793,21 @@
         </is>
       </c>
       <c r="E3" t="n">
-        <v>6425</v>
+        <v>100109</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I3" t="inlineStr"/>
@@ -817,10 +817,10 @@
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>418692</v>
+        <v>418806</v>
       </c>
       <c r="R3" t="n">
-        <v>7045409</v>
+        <v>7045573</v>
       </c>
       <c r="S3" t="n">
         <v>10</v>
@@ -857,7 +857,7 @@
       </c>
       <c r="AC3" t="inlineStr">
         <is>
-          <t>Rikligt</t>
+          <t>Ringhack färska och äldre</t>
         </is>
       </c>
       <c r="AD3" t="b">
@@ -884,10 +884,10 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>117658629</v>
+        <v>117658686</v>
       </c>
       <c r="B4" t="n">
-        <v>57287</v>
+        <v>78480</v>
       </c>
       <c r="C4" t="inlineStr">
         <is>
@@ -900,21 +900,21 @@
         </is>
       </c>
       <c r="E4" t="n">
-        <v>100109</v>
+        <v>6425</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I4" t="inlineStr"/>
@@ -924,10 +924,10 @@
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>418806</v>
+        <v>418692</v>
       </c>
       <c r="R4" t="n">
-        <v>7045573</v>
+        <v>7045409</v>
       </c>
       <c r="S4" t="n">
         <v>10</v>
@@ -964,7 +964,7 @@
       </c>
       <c r="AC4" t="inlineStr">
         <is>
-          <t>Ringhack färska och äldre</t>
+          <t>Rikligt</t>
         </is>
       </c>
       <c r="AD4" t="b">

--- a/artfynd/A 20039-2024 artfynd.xlsx
+++ b/artfynd/A 20039-2024 artfynd.xlsx
@@ -675,10 +675,10 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>117658617</v>
+        <v>117658619</v>
       </c>
       <c r="B2" t="n">
-        <v>90699</v>
+        <v>90499</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>
@@ -687,25 +687,25 @@
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E2" t="n">
-        <v>1106</v>
+        <v>1202</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Vågticka</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Osteina undosa</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>(Peck) Zmitr.</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I2" t="inlineStr"/>
@@ -715,10 +715,10 @@
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>418811</v>
+        <v>418783</v>
       </c>
       <c r="R2" t="n">
-        <v>7045528</v>
+        <v>7045575</v>
       </c>
       <c r="S2" t="n">
         <v>10</v>
@@ -777,7 +777,7 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>117658629</v>
+        <v>117658623</v>
       </c>
       <c r="B3" t="n">
         <v>57287</v>
@@ -817,10 +817,10 @@
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>418806</v>
+        <v>418878</v>
       </c>
       <c r="R3" t="n">
-        <v>7045573</v>
+        <v>7045485</v>
       </c>
       <c r="S3" t="n">
         <v>10</v>
@@ -857,7 +857,7 @@
       </c>
       <c r="AC3" t="inlineStr">
         <is>
-          <t>Ringhack färska och äldre</t>
+          <t>Ringhack</t>
         </is>
       </c>
       <c r="AD3" t="b">
@@ -884,7 +884,7 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>117658686</v>
+        <v>117658688</v>
       </c>
       <c r="B4" t="n">
         <v>78480</v>
@@ -924,10 +924,10 @@
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>418692</v>
+        <v>418767</v>
       </c>
       <c r="R4" t="n">
-        <v>7045409</v>
+        <v>7045599</v>
       </c>
       <c r="S4" t="n">
         <v>10</v>
@@ -991,10 +991,10 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>117658619</v>
+        <v>117658628</v>
       </c>
       <c r="B5" t="n">
-        <v>90499</v>
+        <v>57287</v>
       </c>
       <c r="C5" t="inlineStr">
         <is>
@@ -1007,21 +1007,21 @@
         </is>
       </c>
       <c r="E5" t="n">
-        <v>1202</v>
+        <v>100109</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I5" t="inlineStr"/>
@@ -1031,10 +1031,10 @@
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>418783</v>
+        <v>418684</v>
       </c>
       <c r="R5" t="n">
-        <v>7045575</v>
+        <v>7045562</v>
       </c>
       <c r="S5" t="n">
         <v>10</v>
@@ -1067,6 +1067,11 @@
       <c r="AA5" t="inlineStr">
         <is>
           <t>2024-06-06</t>
+        </is>
+      </c>
+      <c r="AC5" t="inlineStr">
+        <is>
+          <t>Ringhack äldre</t>
         </is>
       </c>
       <c r="AD5" t="b">
@@ -1093,10 +1098,10 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>117658624</v>
+        <v>117658617</v>
       </c>
       <c r="B6" t="n">
-        <v>57287</v>
+        <v>90699</v>
       </c>
       <c r="C6" t="inlineStr">
         <is>
@@ -1105,25 +1110,25 @@
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E6" t="n">
-        <v>100109</v>
+        <v>1106</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Vågticka</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Osteina undosa</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Peck) Zmitr.</t>
         </is>
       </c>
       <c r="I6" t="inlineStr"/>
@@ -1133,10 +1138,10 @@
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>418858</v>
+        <v>418811</v>
       </c>
       <c r="R6" t="n">
-        <v>7045466</v>
+        <v>7045528</v>
       </c>
       <c r="S6" t="n">
         <v>10</v>
@@ -1169,11 +1174,6 @@
       <c r="AA6" t="inlineStr">
         <is>
           <t>2024-06-06</t>
-        </is>
-      </c>
-      <c r="AC6" t="inlineStr">
-        <is>
-          <t>Ringhack äldre</t>
         </is>
       </c>
       <c r="AD6" t="b">
@@ -1200,7 +1200,7 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>117658687</v>
+        <v>117658686</v>
       </c>
       <c r="B7" t="n">
         <v>78480</v>
@@ -1240,10 +1240,10 @@
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>418759</v>
+        <v>418692</v>
       </c>
       <c r="R7" t="n">
-        <v>7045603</v>
+        <v>7045409</v>
       </c>
       <c r="S7" t="n">
         <v>10</v>
@@ -1409,10 +1409,10 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>117658688</v>
+        <v>117658624</v>
       </c>
       <c r="B9" t="n">
-        <v>78480</v>
+        <v>57287</v>
       </c>
       <c r="C9" t="inlineStr">
         <is>
@@ -1425,21 +1425,21 @@
         </is>
       </c>
       <c r="E9" t="n">
-        <v>6425</v>
+        <v>100109</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I9" t="inlineStr"/>
@@ -1449,10 +1449,10 @@
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>418767</v>
+        <v>418858</v>
       </c>
       <c r="R9" t="n">
-        <v>7045599</v>
+        <v>7045466</v>
       </c>
       <c r="S9" t="n">
         <v>10</v>
@@ -1489,7 +1489,7 @@
       </c>
       <c r="AC9" t="inlineStr">
         <is>
-          <t>Rikligt</t>
+          <t>Ringhack äldre</t>
         </is>
       </c>
       <c r="AD9" t="b">
@@ -1618,7 +1618,7 @@
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>117658623</v>
+        <v>117658629</v>
       </c>
       <c r="B11" t="n">
         <v>57287</v>
@@ -1658,10 +1658,10 @@
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>418878</v>
+        <v>418806</v>
       </c>
       <c r="R11" t="n">
-        <v>7045485</v>
+        <v>7045573</v>
       </c>
       <c r="S11" t="n">
         <v>10</v>
@@ -1698,7 +1698,7 @@
       </c>
       <c r="AC11" t="inlineStr">
         <is>
-          <t>Ringhack</t>
+          <t>Ringhack färska och äldre</t>
         </is>
       </c>
       <c r="AD11" t="b">
@@ -1725,10 +1725,10 @@
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>117658628</v>
+        <v>117658687</v>
       </c>
       <c r="B12" t="n">
-        <v>57287</v>
+        <v>78480</v>
       </c>
       <c r="C12" t="inlineStr">
         <is>
@@ -1741,21 +1741,21 @@
         </is>
       </c>
       <c r="E12" t="n">
-        <v>100109</v>
+        <v>6425</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I12" t="inlineStr"/>
@@ -1765,10 +1765,10 @@
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>418684</v>
+        <v>418759</v>
       </c>
       <c r="R12" t="n">
-        <v>7045562</v>
+        <v>7045603</v>
       </c>
       <c r="S12" t="n">
         <v>10</v>
@@ -1805,7 +1805,7 @@
       </c>
       <c r="AC12" t="inlineStr">
         <is>
-          <t>Ringhack äldre</t>
+          <t>Rikligt</t>
         </is>
       </c>
       <c r="AD12" t="b">

--- a/artfynd/A 20039-2024 artfynd.xlsx
+++ b/artfynd/A 20039-2024 artfynd.xlsx
@@ -675,10 +675,10 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>117658619</v>
+        <v>117658624</v>
       </c>
       <c r="B2" t="n">
-        <v>90499</v>
+        <v>57288</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>
@@ -691,21 +691,21 @@
         </is>
       </c>
       <c r="E2" t="n">
-        <v>1202</v>
+        <v>100109</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I2" t="inlineStr"/>
@@ -715,10 +715,10 @@
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>418783</v>
+        <v>418858</v>
       </c>
       <c r="R2" t="n">
-        <v>7045575</v>
+        <v>7045466</v>
       </c>
       <c r="S2" t="n">
         <v>10</v>
@@ -751,6 +751,11 @@
       <c r="AA2" t="inlineStr">
         <is>
           <t>2024-06-06</t>
+        </is>
+      </c>
+      <c r="AC2" t="inlineStr">
+        <is>
+          <t>Ringhack äldre</t>
         </is>
       </c>
       <c r="AD2" t="b">
@@ -777,10 +782,10 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>117658623</v>
+        <v>117658683</v>
       </c>
       <c r="B3" t="n">
-        <v>57287</v>
+        <v>90515</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>
@@ -793,21 +798,21 @@
         </is>
       </c>
       <c r="E3" t="n">
-        <v>100109</v>
+        <v>1204</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Gränsticka</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Phellopilus nigrolimitatus</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Romell) Niemelä, T.Wagner &amp; M.Fisch.</t>
         </is>
       </c>
       <c r="I3" t="inlineStr"/>
@@ -817,10 +822,10 @@
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>418878</v>
+        <v>418571</v>
       </c>
       <c r="R3" t="n">
-        <v>7045485</v>
+        <v>7045427</v>
       </c>
       <c r="S3" t="n">
         <v>10</v>
@@ -853,11 +858,6 @@
       <c r="AA3" t="inlineStr">
         <is>
           <t>2024-06-06</t>
-        </is>
-      </c>
-      <c r="AC3" t="inlineStr">
-        <is>
-          <t>Ringhack</t>
         </is>
       </c>
       <c r="AD3" t="b">
@@ -884,10 +884,10 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>117658688</v>
+        <v>117658628</v>
       </c>
       <c r="B4" t="n">
-        <v>78480</v>
+        <v>57288</v>
       </c>
       <c r="C4" t="inlineStr">
         <is>
@@ -900,21 +900,21 @@
         </is>
       </c>
       <c r="E4" t="n">
-        <v>6425</v>
+        <v>100109</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I4" t="inlineStr"/>
@@ -924,10 +924,10 @@
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>418767</v>
+        <v>418684</v>
       </c>
       <c r="R4" t="n">
-        <v>7045599</v>
+        <v>7045562</v>
       </c>
       <c r="S4" t="n">
         <v>10</v>
@@ -964,7 +964,7 @@
       </c>
       <c r="AC4" t="inlineStr">
         <is>
-          <t>Rikligt</t>
+          <t>Ringhack äldre</t>
         </is>
       </c>
       <c r="AD4" t="b">
@@ -991,10 +991,10 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>117658628</v>
+        <v>117658617</v>
       </c>
       <c r="B5" t="n">
-        <v>57287</v>
+        <v>90701</v>
       </c>
       <c r="C5" t="inlineStr">
         <is>
@@ -1003,25 +1003,25 @@
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E5" t="n">
-        <v>100109</v>
+        <v>1106</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Vågticka</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Osteina undosa</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Peck) Zmitr.</t>
         </is>
       </c>
       <c r="I5" t="inlineStr"/>
@@ -1031,10 +1031,10 @@
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>418684</v>
+        <v>418811</v>
       </c>
       <c r="R5" t="n">
-        <v>7045562</v>
+        <v>7045528</v>
       </c>
       <c r="S5" t="n">
         <v>10</v>
@@ -1067,11 +1067,6 @@
       <c r="AA5" t="inlineStr">
         <is>
           <t>2024-06-06</t>
-        </is>
-      </c>
-      <c r="AC5" t="inlineStr">
-        <is>
-          <t>Ringhack äldre</t>
         </is>
       </c>
       <c r="AD5" t="b">
@@ -1098,10 +1093,10 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>117658617</v>
+        <v>117658629</v>
       </c>
       <c r="B6" t="n">
-        <v>90699</v>
+        <v>57288</v>
       </c>
       <c r="C6" t="inlineStr">
         <is>
@@ -1110,25 +1105,25 @@
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E6" t="n">
-        <v>1106</v>
+        <v>100109</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Vågticka</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Osteina undosa</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>(Peck) Zmitr.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I6" t="inlineStr"/>
@@ -1138,10 +1133,10 @@
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>418811</v>
+        <v>418806</v>
       </c>
       <c r="R6" t="n">
-        <v>7045528</v>
+        <v>7045573</v>
       </c>
       <c r="S6" t="n">
         <v>10</v>
@@ -1174,6 +1169,11 @@
       <c r="AA6" t="inlineStr">
         <is>
           <t>2024-06-06</t>
+        </is>
+      </c>
+      <c r="AC6" t="inlineStr">
+        <is>
+          <t>Ringhack färska och äldre</t>
         </is>
       </c>
       <c r="AD6" t="b">
@@ -1200,10 +1200,10 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>117658686</v>
+        <v>117658688</v>
       </c>
       <c r="B7" t="n">
-        <v>78480</v>
+        <v>78482</v>
       </c>
       <c r="C7" t="inlineStr">
         <is>
@@ -1240,10 +1240,10 @@
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>418692</v>
+        <v>418767</v>
       </c>
       <c r="R7" t="n">
-        <v>7045409</v>
+        <v>7045599</v>
       </c>
       <c r="S7" t="n">
         <v>10</v>
@@ -1307,10 +1307,10 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>117658683</v>
+        <v>117658686</v>
       </c>
       <c r="B8" t="n">
-        <v>90513</v>
+        <v>78482</v>
       </c>
       <c r="C8" t="inlineStr">
         <is>
@@ -1323,21 +1323,21 @@
         </is>
       </c>
       <c r="E8" t="n">
-        <v>1204</v>
+        <v>6425</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Gränsticka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Phellopilus nigrolimitatus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>(Romell) Niemelä, T.Wagner &amp; M.Fisch.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I8" t="inlineStr"/>
@@ -1347,10 +1347,10 @@
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>418571</v>
+        <v>418692</v>
       </c>
       <c r="R8" t="n">
-        <v>7045427</v>
+        <v>7045409</v>
       </c>
       <c r="S8" t="n">
         <v>10</v>
@@ -1383,6 +1383,11 @@
       <c r="AA8" t="inlineStr">
         <is>
           <t>2024-06-06</t>
+        </is>
+      </c>
+      <c r="AC8" t="inlineStr">
+        <is>
+          <t>Rikligt</t>
         </is>
       </c>
       <c r="AD8" t="b">
@@ -1409,10 +1414,10 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>117658624</v>
+        <v>117658619</v>
       </c>
       <c r="B9" t="n">
-        <v>57287</v>
+        <v>90501</v>
       </c>
       <c r="C9" t="inlineStr">
         <is>
@@ -1425,21 +1430,21 @@
         </is>
       </c>
       <c r="E9" t="n">
-        <v>100109</v>
+        <v>1202</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I9" t="inlineStr"/>
@@ -1449,10 +1454,10 @@
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>418858</v>
+        <v>418783</v>
       </c>
       <c r="R9" t="n">
-        <v>7045466</v>
+        <v>7045575</v>
       </c>
       <c r="S9" t="n">
         <v>10</v>
@@ -1485,11 +1490,6 @@
       <c r="AA9" t="inlineStr">
         <is>
           <t>2024-06-06</t>
-        </is>
-      </c>
-      <c r="AC9" t="inlineStr">
-        <is>
-          <t>Ringhack äldre</t>
         </is>
       </c>
       <c r="AD9" t="b">
@@ -1516,10 +1516,10 @@
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>117658618</v>
+        <v>117658623</v>
       </c>
       <c r="B10" t="n">
-        <v>90499</v>
+        <v>57288</v>
       </c>
       <c r="C10" t="inlineStr">
         <is>
@@ -1532,21 +1532,21 @@
         </is>
       </c>
       <c r="E10" t="n">
-        <v>1202</v>
+        <v>100109</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I10" t="inlineStr"/>
@@ -1556,10 +1556,10 @@
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>418632</v>
+        <v>418878</v>
       </c>
       <c r="R10" t="n">
-        <v>7045522</v>
+        <v>7045485</v>
       </c>
       <c r="S10" t="n">
         <v>10</v>
@@ -1592,6 +1592,11 @@
       <c r="AA10" t="inlineStr">
         <is>
           <t>2024-06-06</t>
+        </is>
+      </c>
+      <c r="AC10" t="inlineStr">
+        <is>
+          <t>Ringhack</t>
         </is>
       </c>
       <c r="AD10" t="b">
@@ -1618,10 +1623,10 @@
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>117658629</v>
+        <v>117658687</v>
       </c>
       <c r="B11" t="n">
-        <v>57287</v>
+        <v>78482</v>
       </c>
       <c r="C11" t="inlineStr">
         <is>
@@ -1634,21 +1639,21 @@
         </is>
       </c>
       <c r="E11" t="n">
-        <v>100109</v>
+        <v>6425</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I11" t="inlineStr"/>
@@ -1658,10 +1663,10 @@
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>418806</v>
+        <v>418759</v>
       </c>
       <c r="R11" t="n">
-        <v>7045573</v>
+        <v>7045603</v>
       </c>
       <c r="S11" t="n">
         <v>10</v>
@@ -1698,7 +1703,7 @@
       </c>
       <c r="AC11" t="inlineStr">
         <is>
-          <t>Ringhack färska och äldre</t>
+          <t>Rikligt</t>
         </is>
       </c>
       <c r="AD11" t="b">
@@ -1725,10 +1730,10 @@
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>117658687</v>
+        <v>117658618</v>
       </c>
       <c r="B12" t="n">
-        <v>78480</v>
+        <v>90501</v>
       </c>
       <c r="C12" t="inlineStr">
         <is>
@@ -1741,21 +1746,21 @@
         </is>
       </c>
       <c r="E12" t="n">
-        <v>6425</v>
+        <v>1202</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I12" t="inlineStr"/>
@@ -1765,10 +1770,10 @@
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>418759</v>
+        <v>418632</v>
       </c>
       <c r="R12" t="n">
-        <v>7045603</v>
+        <v>7045522</v>
       </c>
       <c r="S12" t="n">
         <v>10</v>
@@ -1801,11 +1806,6 @@
       <c r="AA12" t="inlineStr">
         <is>
           <t>2024-06-06</t>
-        </is>
-      </c>
-      <c r="AC12" t="inlineStr">
-        <is>
-          <t>Rikligt</t>
         </is>
       </c>
       <c r="AD12" t="b">
